--- a/comp364-schedule-8-29-2026.xlsx
+++ b/comp364-schedule-8-29-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jmac\git\comp364-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2314773-39FD-4CDB-AD1F-F25B05F450FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C091B908-C604-4E9F-94B8-9396A2195CFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="119">
   <si>
     <t>Class number</t>
   </si>
@@ -515,6 +515,12 @@
   </si>
   <si>
     <t xml:space="preserve">Transformers in Pytorch </t>
+  </si>
+  <si>
+    <t>The Chinese room argument</t>
+  </si>
+  <si>
+    <t>Computationalism</t>
   </si>
 </sst>
 </file>
@@ -773,7 +779,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -894,13 +900,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -910,6 +910,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -917,29 +920,62 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -953,47 +989,14 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1303,20 +1306,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.140625" style="8" customWidth="1"/>
-    <col min="2" max="2" width="5.140625" style="18" customWidth="1"/>
-    <col min="3" max="3" width="6.42578125" style="13" customWidth="1"/>
-    <col min="4" max="4" width="21.28515625" style="7" customWidth="1"/>
-    <col min="5" max="5" width="7.5703125" style="8" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" style="8" customWidth="1"/>
-    <col min="7" max="7" width="34.42578125" style="6" customWidth="1"/>
-    <col min="8" max="8" width="34.7109375" style="38" customWidth="1"/>
-    <col min="9" max="9" width="37.85546875" customWidth="1"/>
+    <col min="1" max="1" width="6.1796875" style="8" customWidth="1"/>
+    <col min="2" max="2" width="5.1796875" style="18" customWidth="1"/>
+    <col min="3" max="3" width="6.453125" style="13" customWidth="1"/>
+    <col min="4" max="4" width="21.26953125" style="7" customWidth="1"/>
+    <col min="5" max="5" width="7.54296875" style="8" customWidth="1"/>
+    <col min="6" max="6" width="11.7265625" style="8" customWidth="1"/>
+    <col min="7" max="7" width="34.453125" style="6" customWidth="1"/>
+    <col min="8" max="8" width="34.7265625" style="38" customWidth="1"/>
+    <col min="9" max="9" width="37.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="6" customFormat="1" ht="24" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>32</v>
       </c>
@@ -1335,16 +1338,16 @@
       <c r="F1" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="G1" s="44" t="s">
+      <c r="G1" s="42" t="s">
         <v>95</v>
       </c>
-      <c r="H1" s="45" t="s">
+      <c r="H1" s="43" t="s">
         <v>42</v>
       </c>
       <c r="I1"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="47">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" s="46">
         <v>1</v>
       </c>
       <c r="B2" s="16" t="s">
@@ -1353,7 +1356,7 @@
       <c r="C2" s="14">
         <v>46266</v>
       </c>
-      <c r="D2" s="61" t="s">
+      <c r="D2" s="49" t="s">
         <v>48</v>
       </c>
       <c r="E2" s="5" t="s">
@@ -1365,8 +1368,8 @@
       </c>
       <c r="H2" s="33"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="48"/>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" s="47"/>
       <c r="B3" s="16" t="s">
         <v>35</v>
       </c>
@@ -1374,7 +1377,7 @@
         <f>C2+3</f>
         <v>46269</v>
       </c>
-      <c r="D3" s="63"/>
+      <c r="D3" s="50"/>
       <c r="E3" s="5" t="s">
         <v>6</v>
       </c>
@@ -1386,8 +1389,8 @@
         <v>106</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="47">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="46">
         <f>A2+1</f>
         <v>2</v>
       </c>
@@ -1399,18 +1402,18 @@
         <f>C2+7</f>
         <v>46273</v>
       </c>
-      <c r="D4" s="65" t="s">
+      <c r="D4" s="51" t="s">
         <v>83</v>
       </c>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
       <c r="G4" s="21"/>
       <c r="H4" s="33" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="48"/>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="47"/>
       <c r="B5" s="16" t="str">
         <f>B3</f>
         <v>Fri</v>
@@ -1419,7 +1422,7 @@
         <f>C3+7</f>
         <v>46276</v>
       </c>
-      <c r="D5" s="64" t="s">
+      <c r="D5" s="45" t="s">
         <v>46</v>
       </c>
       <c r="E5" s="5" t="s">
@@ -1435,8 +1438,8 @@
         <v>107</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="47">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" s="46">
         <f t="shared" ref="A6" si="0">A4+1</f>
         <v>3</v>
       </c>
@@ -1448,7 +1451,7 @@
         <f t="shared" ref="C6:C35" si="2">C4+7</f>
         <v>46280</v>
       </c>
-      <c r="D6" s="64"/>
+      <c r="D6" s="45"/>
       <c r="E6" s="5" t="s">
         <v>8</v>
       </c>
@@ -1462,8 +1465,8 @@
         <v>92</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="48"/>
+    <row r="7" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="A7" s="47"/>
       <c r="B7" s="16" t="str">
         <f t="shared" si="1"/>
         <v>Fri</v>
@@ -1486,8 +1489,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="47">
+    <row r="8" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="A8" s="46">
         <f t="shared" ref="A8" si="3">A6+1</f>
         <v>4</v>
       </c>
@@ -1499,7 +1502,7 @@
         <f t="shared" si="2"/>
         <v>46287</v>
       </c>
-      <c r="D8" s="64" t="s">
+      <c r="D8" s="45" t="s">
         <v>47</v>
       </c>
       <c r="E8" s="5" t="s">
@@ -1515,8 +1518,8 @@
         <v>108</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="48"/>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" s="47"/>
       <c r="B9" s="16" t="str">
         <f t="shared" si="1"/>
         <v>Fri</v>
@@ -1525,7 +1528,7 @@
         <f t="shared" si="2"/>
         <v>46290</v>
       </c>
-      <c r="D9" s="64"/>
+      <c r="D9" s="45"/>
       <c r="E9" s="5" t="s">
         <v>11</v>
       </c>
@@ -1539,20 +1542,20 @@
         <v>72</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="47">
+    <row r="10" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="46">
         <f>A8+1</f>
         <v>5</v>
       </c>
-      <c r="B10" s="47" t="str">
+      <c r="B10" s="46" t="str">
         <f>B8</f>
         <v>Tue</v>
       </c>
-      <c r="C10" s="66">
+      <c r="C10" s="52">
         <f>C8+7</f>
         <v>46294</v>
       </c>
-      <c r="D10" s="61" t="s">
+      <c r="D10" s="49" t="s">
         <v>61</v>
       </c>
       <c r="E10" s="5" t="s">
@@ -1566,20 +1569,20 @@
         <v>84</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="52"/>
-      <c r="B11" s="48"/>
-      <c r="C11" s="67"/>
-      <c r="D11" s="62"/>
-      <c r="E11" s="49" t="s">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" s="48"/>
+      <c r="B11" s="47"/>
+      <c r="C11" s="53"/>
+      <c r="D11" s="71"/>
+      <c r="E11" s="57" t="s">
         <v>85</v>
       </c>
-      <c r="F11" s="50"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="51"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="48"/>
+      <c r="F11" s="58"/>
+      <c r="G11" s="58"/>
+      <c r="H11" s="59"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" s="47"/>
       <c r="B12" s="16" t="str">
         <f>B9</f>
         <v>Fri</v>
@@ -1588,7 +1591,7 @@
         <f>C9+7</f>
         <v>46297</v>
       </c>
-      <c r="D12" s="62"/>
+      <c r="D12" s="71"/>
       <c r="E12" s="5" t="s">
         <v>13</v>
       </c>
@@ -1602,8 +1605,8 @@
         <v>73</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="51" x14ac:dyDescent="0.25">
-      <c r="A13" s="47">
+    <row r="13" spans="1:9" ht="38.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="46">
         <f t="shared" ref="A13" si="4">A10+1</f>
         <v>6</v>
       </c>
@@ -1615,7 +1618,7 @@
         <f>C10+7</f>
         <v>46301</v>
       </c>
-      <c r="D13" s="63"/>
+      <c r="D13" s="50"/>
       <c r="E13" s="5" t="s">
         <v>14</v>
       </c>
@@ -1627,8 +1630,8 @@
       </c>
       <c r="H13" s="33"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="48"/>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14" s="47"/>
       <c r="B14" s="16" t="str">
         <f t="shared" si="1"/>
         <v>Fri</v>
@@ -1646,13 +1649,13 @@
       <c r="F14" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="G14" s="46" t="s">
+      <c r="G14" s="44" t="s">
         <v>104</v>
       </c>
       <c r="H14" s="33"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="47">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15" s="46">
         <f t="shared" ref="A15" si="5">A13+1</f>
         <v>7</v>
       </c>
@@ -1671,13 +1674,13 @@
         <v>16</v>
       </c>
       <c r="F15" s="10"/>
-      <c r="G15" s="46" t="s">
+      <c r="G15" s="44" t="s">
         <v>104</v>
       </c>
       <c r="H15" s="34"/>
     </row>
-    <row r="16" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="48"/>
+    <row r="16" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="A16" s="47"/>
       <c r="B16" s="16" t="str">
         <f t="shared" si="1"/>
         <v>Fri</v>
@@ -1700,7 +1703,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="10"/>
       <c r="B17" s="16" t="str">
         <f t="shared" si="1"/>
@@ -1713,13 +1716,13 @@
       <c r="D17" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="E17" s="68"/>
-      <c r="F17" s="69"/>
-      <c r="G17" s="69"/>
-      <c r="H17" s="70"/>
-    </row>
-    <row r="18" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="47">
+      <c r="E17" s="54"/>
+      <c r="F17" s="55"/>
+      <c r="G17" s="55"/>
+      <c r="H17" s="56"/>
+    </row>
+    <row r="18" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A18" s="46">
         <v>8</v>
       </c>
       <c r="B18" s="16" t="str">
@@ -1730,7 +1733,7 @@
         <f t="shared" si="2"/>
         <v>46318</v>
       </c>
-      <c r="D18" s="64" t="s">
+      <c r="D18" s="45" t="s">
         <v>40</v>
       </c>
       <c r="E18" s="5" t="s">
@@ -1744,17 +1747,17 @@
         <v>109</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="52"/>
-      <c r="B19" s="57" t="str">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" s="48"/>
+      <c r="B19" s="67" t="str">
         <f>B17</f>
         <v>Tue</v>
       </c>
-      <c r="C19" s="59">
+      <c r="C19" s="69">
         <f>C17+7</f>
         <v>46322</v>
       </c>
-      <c r="D19" s="64"/>
+      <c r="D19" s="45"/>
       <c r="E19" s="5" t="s">
         <v>19</v>
       </c>
@@ -1766,20 +1769,20 @@
         <v>75</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="48"/>
-      <c r="B20" s="58"/>
-      <c r="C20" s="60"/>
-      <c r="D20" s="64"/>
-      <c r="E20" s="71" t="s">
+    <row r="20" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="47"/>
+      <c r="B20" s="68"/>
+      <c r="C20" s="70"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="F20" s="72"/>
-      <c r="G20" s="72"/>
-      <c r="H20" s="73"/>
-    </row>
-    <row r="21" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="47">
+      <c r="F20" s="65"/>
+      <c r="G20" s="65"/>
+      <c r="H20" s="66"/>
+    </row>
+    <row r="21" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="46">
         <v>9</v>
       </c>
       <c r="B21" s="39" t="s">
@@ -1788,16 +1791,16 @@
       <c r="C21" s="40">
         <v>46324</v>
       </c>
-      <c r="D21" s="64"/>
-      <c r="E21" s="65" t="s">
+      <c r="D21" s="45"/>
+      <c r="E21" s="51" t="s">
         <v>88</v>
       </c>
-      <c r="F21" s="65"/>
-      <c r="G21" s="65"/>
-      <c r="H21" s="65"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="52"/>
+      <c r="F21" s="51"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="51"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" s="48"/>
       <c r="B22" s="16" t="str">
         <f>B18</f>
         <v>Fri</v>
@@ -1806,7 +1809,7 @@
         <f>C18+7</f>
         <v>46325</v>
       </c>
-      <c r="D22" s="64"/>
+      <c r="D22" s="45"/>
       <c r="E22" s="5" t="s">
         <v>20</v>
       </c>
@@ -1818,8 +1821,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="48"/>
+    <row r="23" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A23" s="47"/>
       <c r="B23" s="16" t="str">
         <f>B19</f>
         <v>Tue</v>
@@ -1835,15 +1838,15 @@
         <v>21</v>
       </c>
       <c r="F23" s="25"/>
-      <c r="G23" s="74" t="s">
+      <c r="G23" s="21" t="s">
         <v>113</v>
       </c>
       <c r="H23" s="33" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="47">
+    <row r="24" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A24" s="46">
         <v>10</v>
       </c>
       <c r="B24" s="16" t="str">
@@ -1868,8 +1871,8 @@
       </c>
       <c r="H24" s="33"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="48"/>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A25" s="47"/>
       <c r="B25" s="16" t="str">
         <f t="shared" si="1"/>
         <v>Tue</v>
@@ -1878,7 +1881,7 @@
         <f t="shared" si="2"/>
         <v>46336</v>
       </c>
-      <c r="D25" s="64" t="s">
+      <c r="D25" s="45" t="s">
         <v>65</v>
       </c>
       <c r="E25" s="5" t="s">
@@ -1892,8 +1895,8 @@
       </c>
       <c r="H25" s="34"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="54">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A26" s="60">
         <f>A24+1</f>
         <v>11</v>
       </c>
@@ -1903,16 +1906,16 @@
       <c r="C26" s="14">
         <v>46337</v>
       </c>
-      <c r="D26" s="64"/>
-      <c r="E26" s="53" t="s">
+      <c r="D26" s="45"/>
+      <c r="E26" s="63" t="s">
         <v>90</v>
       </c>
-      <c r="F26" s="53"/>
-      <c r="G26" s="53"/>
-      <c r="H26" s="53"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="55"/>
+      <c r="F26" s="63"/>
+      <c r="G26" s="63"/>
+      <c r="H26" s="63"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A27" s="61"/>
       <c r="B27" s="16" t="str">
         <f>B24</f>
         <v>Fri</v>
@@ -1921,7 +1924,7 @@
         <f>C24+7</f>
         <v>46339</v>
       </c>
-      <c r="D27" s="64"/>
+      <c r="D27" s="45"/>
       <c r="E27" s="5" t="s">
         <v>24</v>
       </c>
@@ -1933,8 +1936,8 @@
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="56"/>
+    <row r="28" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A28" s="62"/>
       <c r="B28" s="16" t="str">
         <f>B25</f>
         <v>Tue</v>
@@ -1950,13 +1953,15 @@
         <v>25</v>
       </c>
       <c r="F28" s="21"/>
-      <c r="G28" s="21"/>
+      <c r="G28" s="21" t="s">
+        <v>117</v>
+      </c>
       <c r="H28" s="33" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="47">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A29" s="46">
         <f>A26+1</f>
         <v>12</v>
       </c>
@@ -1977,11 +1982,13 @@
       <c r="F29" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="G29" s="21"/>
+      <c r="G29" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="H29" s="34"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="48"/>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30" s="47"/>
       <c r="B30" s="16" t="str">
         <f t="shared" si="1"/>
         <v>Tue</v>
@@ -1999,12 +2006,14 @@
       <c r="F30" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="G30" s="21"/>
+      <c r="G30" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="H30" s="33" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="10"/>
       <c r="B31" s="16" t="str">
         <f t="shared" si="1"/>
@@ -2022,8 +2031,8 @@
       <c r="G31" s="21"/>
       <c r="H31" s="33"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="47">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A32" s="46">
         <f>A29+1</f>
         <v>13</v>
       </c>
@@ -2042,11 +2051,13 @@
         <v>28</v>
       </c>
       <c r="F32" s="10"/>
-      <c r="G32" s="21"/>
+      <c r="G32" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="H32" s="36"/>
     </row>
-    <row r="33" spans="1:9" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="48"/>
+    <row r="33" spans="1:9" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="47"/>
       <c r="B33" s="17" t="str">
         <f t="shared" si="1"/>
         <v>Fri</v>
@@ -2064,14 +2075,16 @@
       <c r="F33" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="G33" s="41"/>
+      <c r="G33" s="72" t="s">
+        <v>104</v>
+      </c>
       <c r="H33" s="33" t="s">
         <v>80</v>
       </c>
       <c r="I33"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="47">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A34" s="46">
         <f t="shared" ref="A34" si="6">A32+1</f>
         <v>14</v>
       </c>
@@ -2090,13 +2103,15 @@
         <v>30</v>
       </c>
       <c r="F34" s="19"/>
-      <c r="G34" s="42"/>
+      <c r="G34" s="41" t="s">
+        <v>118</v>
+      </c>
       <c r="H34" s="33" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="48"/>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A35" s="47"/>
       <c r="B35" s="16" t="str">
         <f t="shared" si="1"/>
         <v>Fri</v>
@@ -2114,10 +2129,12 @@
       <c r="F35" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="G35" s="43"/>
+      <c r="G35" s="73" t="s">
+        <v>104</v>
+      </c>
       <c r="H35" s="34"/>
     </row>
-    <row r="36" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" ht="39" x14ac:dyDescent="0.35">
       <c r="A36" s="10"/>
       <c r="B36" s="16" t="s">
         <v>35</v>
@@ -2135,29 +2152,15 @@
       <c r="G36" s="21"/>
       <c r="H36" s="33"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="F37" s="6"/>
       <c r="H37" s="37"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="D39"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="D25:D27"/>
-    <mergeCell ref="D18:D22"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E17:H17"/>
     <mergeCell ref="A29:A30"/>
     <mergeCell ref="A32:A33"/>
     <mergeCell ref="A34:A35"/>
@@ -2174,6 +2177,20 @@
     <mergeCell ref="B19:B20"/>
     <mergeCell ref="C19:C20"/>
     <mergeCell ref="D10:D13"/>
+    <mergeCell ref="D25:D27"/>
+    <mergeCell ref="D18:D22"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E17:H17"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
